--- a/tables/table_jurs_available_per_country.xlsx
+++ b/tables/table_jurs_available_per_country.xlsx
@@ -151,7 +151,7 @@
     <t>CZE</t>
   </si>
   <si>
-    <t>COU</t>
+    <t>count</t>
   </si>
 </sst>
 </file>
